--- a/data/berita_antara_2026-08-01.xlsx
+++ b/data/berita_antara_2026-08-01.xlsx
@@ -471,66 +471,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
+          <t>Kapal KM Princes Soya terbakar di Pelabuhan Samarinda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
+          <t>Sat, 01 Aug 2026 17:00:58 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
+          <t>Api membakar kabin kapal penumpang KM Prince Soya di Pelabuhan Samarinda, Kalimantan Timur.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
+          <t>https://www.antaranews.com/foto/5675799/kapal-km-princes-soya-terbakar-di-pelabuhan-samarinda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-kapal-Prince-Soya-di-Pelabuhan-Samarinda-010826-Pelindo-AP-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
+          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
+          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
+          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
+          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
         </is>
       </c>
     </row>
@@ -542,28 +542,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
+          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
+          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
+          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
+          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
         </is>
       </c>
     </row>
@@ -575,28 +575,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
+          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
+          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
+          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
+          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
         </is>
       </c>
     </row>
@@ -608,61 +608,61 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
+          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
+          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
+          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
+          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
+          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
+          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
+          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
         </is>
       </c>
     </row>
@@ -674,94 +674,94 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
+          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
+          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
+          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
+          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
+          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
+          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
+          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
+          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
+          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
+          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
+          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
+          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
+          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
+          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
+          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
+          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
         </is>
       </c>
     </row>
@@ -806,61 +806,61 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10 kebiasaan kecil yang bisa meningkatkan kualitas hidup sehari-hari</t>
+          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:53:11 +0700</t>
+          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Menjalani hidup yang lebih baik tidak selalu membutuhkan perubahan besar. Justru, kebiasaan-kebiasaan kecil yang ...</t>
+          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675683/10-kebiasaan-kecil-yang-bisa-meningkatkan-kualitas-hidup-sehari-hari</t>
+          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/24/skrining-kebugaran-jasmani-asn-kota-bogor-2810969.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
+          <t>10 kebiasaan kecil yang bisa meningkatkan kualitas hidup sehari-hari</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
+          <t>Sat, 01 Aug 2026 14:53:11 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
+          <t>Menjalani hidup yang lebih baik tidak selalu membutuhkan perubahan besar. Justru, kebiasaan-kebiasaan kecil yang ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
+          <t>https://www.antaranews.com/berita/5675683/10-kebiasaan-kecil-yang-bisa-meningkatkan-kualitas-hidup-sehari-hari</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/24/skrining-kebugaran-jasmani-asn-kota-bogor-2810969.jpg</t>
         </is>
       </c>
     </row>
@@ -872,28 +872,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
+          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
+          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
+          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
         </is>
       </c>
     </row>
@@ -905,28 +905,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
+          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
+          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
+          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
+          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
         </is>
       </c>
     </row>
@@ -938,28 +938,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Begini kondisi kebakaran lahan di Indralaya Utara Sumsel</t>
+          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 21:32:25 +0700</t>
+          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foto udara petugas bersama warga berusaha memadamkan kebakaran lahan yang berada di dekat rumahnya di Desa Sungai Rambutan, Indralaya Utara, Ogan Ili (OI), Sumatera Selatan.</t>
+          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676076/begini-kondisi-kebakaran-lahan-di-indralaya-utara-sumsel</t>
+          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-Lahan-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
         </is>
       </c>
     </row>
@@ -971,28 +971,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sudah sepekan petugas berjibaku padamkan karhutla di Kubu Raya</t>
+          <t>Begini kondisi kebakaran lahan di Indralaya Utara Sumsel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 20:51:18 +0700</t>
+          <t>Sat, 01 Aug 2026 21:32:25 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Personel BPBD Kabupaten Kubu Raya menyemprotkan air ke lahan gambut yang terbakar di Dusun Sidomulyo, Desa Limbung, Kecamatan Sungai Raya, Kabupaten Kubu Raya, Kalimantan Barat.</t>
+          <t>Foto udara petugas bersama warga berusaha memadamkan kebakaran lahan yang berada di dekat rumahnya di Desa Sungai Rambutan, Indralaya Utara, Ogan Ili (OI), Sumatera Selatan.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676039/sudah-sepekan-petugas-berjibaku-padamkan-karhutla-di-kubu-raya</t>
+          <t>https://www.antaranews.com/foto/5676076/begini-kondisi-kebakaran-lahan-di-indralaya-utara-sumsel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-Lahan-4.jpg</t>
         </is>
       </c>
     </row>
@@ -1004,28 +1004,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pergelaran kesenian balaganjur pada hari suci umat Hindu di Bali</t>
+          <t>Sudah sepekan petugas berjibaku padamkan karhutla di Kubu Raya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 20:11:17 +0700</t>
+          <t>Sat, 01 Aug 2026 20:51:18 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sejumlah pemuda menampilkan kesenian baleganjur pada Hari Suci Tumpek Krulut di The Blooms Bali, Tabanan, Bali.</t>
+          <t>Personel BPBD Kabupaten Kubu Raya menyemprotkan air ke lahan gambut yang terbakar di Dusun Sidomulyo, Desa Limbung, Kecamatan Sungai Raya, Kabupaten Kubu Raya, Kalimantan Barat.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676007/pergelaran-kesenian-balaganjur-pada-hari-suci-umat-hindu-di-bali</t>
+          <t>https://www.antaranews.com/foto/5676039/sudah-sepekan-petugas-berjibaku-padamkan-karhutla-di-kubu-raya</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bali-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1037,28 +1037,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bungkam PSMS Medan 4-1, Persija Jakarta buka kans ke semifinal Piala Presiden</t>
+          <t>Pergelaran kesenian balaganjur pada hari suci umat Hindu di Bali</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 19:04:32 +0700</t>
+          <t>Sat, 01 Aug 2026 20:11:17 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pesepak bola Persija Jakarta Denis Kolinger (kanan) berebut bola udara dengan pesepak bola PSMS Medan Angelo Meneses (kiri) dan Asyraq Gufron (tengah) pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur.</t>
+          <t>Sejumlah pemuda menampilkan kesenian baleganjur pada Hari Suci Tumpek Krulut di The Blooms Bali, Tabanan, Bali.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5675900/bungkam-psms-medan-4-1-persija-jakarta-buka-kans-ke-semifinal-piala-presiden</t>
+          <t>https://www.antaranews.com/foto/5676007/pergelaran-kesenian-balaganjur-pada-hari-suci-umat-hindu-di-bali</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bola-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bali-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1070,28 +1070,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pemasangan jaring apung penahan sampah di Sungai Lestari</t>
+          <t>Bungkam PSMS Medan 4-1, Persija Jakarta buka kans ke semifinal Piala Presiden</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 18:17:45 +0700</t>
+          <t>Sat, 01 Aug 2026 19:04:32 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Relawan sungai memasang jaring terapung penahan sampah atau trash boom di Sungai Jenes, Pajang, Laweyan, Solo, Jawa Tengah, Sabtu (1/8/2026). Pemkot Solo bekerja sama dengan United Nations Development Programme (UNDP) dan Clean Rivers meluncurkan program penanganan sampah Sungai Lestari dengan skema sampah yang diambil dari hulu sungai Kota Solo akan langsung dipilah dan diolah oleh mitra lokal hingga diharapkan mampu menciptakan sungai yang yang bersih sekaligus upaya mengurangi beban kuota sampah di TPA Putri Cempo. ANTARA FOTO/Mohammad Ayudha/YU</t>
+          <t>Pesepak bola Persija Jakarta Denis Kolinger (kanan) berebut bola udara dengan pesepak bola PSMS Medan Angelo Meneses (kiri) dan Asyraq Gufron (tengah) pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5675871/pemasangan-jaring-apung-penahan-sampah-di-sungai-lestari</t>
+          <t>https://www.antaranews.com/foto/5675900/bungkam-psms-medan-4-1-persija-jakarta-buka-kans-ke-semifinal-piala-presiden</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/pemasangan-trash-boom-penahan-sampah-010826-yud-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bola-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1103,28 +1103,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Begini kemeriahan Jakarta Watersport Festival 2026 di Danau Sunter</t>
+          <t>Pemasangan jaring apung penahan sampah di Sungai Lestari</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 18:01:11 +0700</t>
+          <t>Sat, 01 Aug 2026 18:17:45 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Peserta beradu kecepatan saat mengikuti lomba perahu naga pada Jakarta Watersport Festival 2026 di Danau Sunter, Jakarta.</t>
+          <t>Relawan sungai memasang jaring terapung penahan sampah atau trash boom di Sungai Jenes, Pajang, Laweyan, Solo, Jawa Tengah, Sabtu (1/8/2026). Pemkot Solo bekerja sama dengan United Nations Development Programme (UNDP) dan Clean Rivers meluncurkan program penanganan sampah Sungai Lestari dengan skema sampah yang diambil dari hulu sungai Kota Solo akan langsung dipilah dan diolah oleh mitra lokal hingga diharapkan mampu menciptakan sungai yang yang bersih sekaligus upaya mengurangi beban kuota sampah di TPA Putri Cempo. ANTARA FOTO/Mohammad Ayudha/YU</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5675857/begini-kemeriahan-jakarta-watersport-festival-2026-di-danau-sunter</t>
+          <t>https://www.antaranews.com/foto/5675871/pemasangan-jaring-apung-penahan-sampah-di-sungai-lestari</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Jakarta-Watersport-Festival-2026-182026-pma-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/pemasangan-trash-boom-penahan-sampah-010826-yud-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1136,28 +1136,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kapal KM Princes Soya terbakar di Pelabuhan Samarinda</t>
+          <t>Begini kemeriahan Jakarta Watersport Festival 2026 di Danau Sunter</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 17:00:58 +0700</t>
+          <t>Sat, 01 Aug 2026 18:01:11 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Api membakar kabin kapal penumpang KM Prince Soya di Pelabuhan Samarinda, Kalimantan Timur.</t>
+          <t>Peserta beradu kecepatan saat mengikuti lomba perahu naga pada Jakarta Watersport Festival 2026 di Danau Sunter, Jakarta.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5675799/kapal-km-princes-soya-terbakar-di-pelabuhan-samarinda</t>
+          <t>https://www.antaranews.com/foto/5675857/begini-kemeriahan-jakarta-watersport-festival-2026-di-danau-sunter</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-kapal-Prince-Soya-di-Pelabuhan-Samarinda-010826-Pelindo-AP-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Jakarta-Watersport-Festival-2026-182026-pma-2.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-01.xlsx
+++ b/data/berita_antara_2026-08-01.xlsx
@@ -504,66 +504,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
+          <t>Begini kemeriahan Jakarta Watersport Festival 2026 di Danau Sunter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
+          <t>Sat, 01 Aug 2026 18:01:11 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
+          <t>Peserta beradu kecepatan saat mengikuti lomba perahu naga pada Jakarta Watersport Festival 2026 di Danau Sunter, Jakarta.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
+          <t>https://www.antaranews.com/foto/5675857/begini-kemeriahan-jakarta-watersport-festival-2026-di-danau-sunter</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Jakarta-Watersport-Festival-2026-182026-pma-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
+          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
+          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
+          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
+          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
         </is>
       </c>
     </row>
@@ -575,28 +575,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
+          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
+          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
+          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
+          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
         </is>
       </c>
     </row>
@@ -608,28 +608,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
+          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
+          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
+          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
+          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
         </is>
       </c>
     </row>
@@ -641,61 +641,61 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
+          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
+          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
+          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
+          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
+          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
+          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
+          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
         </is>
       </c>
     </row>
@@ -707,94 +707,94 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
+          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
+          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
+          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
+          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
+          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
+          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
+          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
+          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
+          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
+          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
+          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
+          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
         </is>
       </c>
     </row>
@@ -806,28 +806,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
+          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
+          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
+          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
+          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
         </is>
       </c>
     </row>
@@ -839,61 +839,61 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10 kebiasaan kecil yang bisa meningkatkan kualitas hidup sehari-hari</t>
+          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:53:11 +0700</t>
+          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Menjalani hidup yang lebih baik tidak selalu membutuhkan perubahan besar. Justru, kebiasaan-kebiasaan kecil yang ...</t>
+          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675683/10-kebiasaan-kecil-yang-bisa-meningkatkan-kualitas-hidup-sehari-hari</t>
+          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/24/skrining-kebugaran-jasmani-asn-kota-bogor-2810969.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
+          <t>10 kebiasaan kecil yang bisa meningkatkan kualitas hidup sehari-hari</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
+          <t>Sat, 01 Aug 2026 14:53:11 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
+          <t>Menjalani hidup yang lebih baik tidak selalu membutuhkan perubahan besar. Justru, kebiasaan-kebiasaan kecil yang ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
+          <t>https://www.antaranews.com/berita/5675683/10-kebiasaan-kecil-yang-bisa-meningkatkan-kualitas-hidup-sehari-hari</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/24/skrining-kebugaran-jasmani-asn-kota-bogor-2810969.jpg</t>
         </is>
       </c>
     </row>
@@ -905,28 +905,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
+          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
+          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
+          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
         </is>
       </c>
     </row>
@@ -938,28 +938,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
+          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
+          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
+          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
+          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
         </is>
       </c>
     </row>
@@ -971,28 +971,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Begini kondisi kebakaran lahan di Indralaya Utara Sumsel</t>
+          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 21:32:25 +0700</t>
+          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foto udara petugas bersama warga berusaha memadamkan kebakaran lahan yang berada di dekat rumahnya di Desa Sungai Rambutan, Indralaya Utara, Ogan Ili (OI), Sumatera Selatan.</t>
+          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676076/begini-kondisi-kebakaran-lahan-di-indralaya-utara-sumsel</t>
+          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-Lahan-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1004,28 +1004,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sudah sepekan petugas berjibaku padamkan karhutla di Kubu Raya</t>
+          <t>Begini kondisi kebakaran lahan di Indralaya Utara Sumsel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 20:51:18 +0700</t>
+          <t>Sat, 01 Aug 2026 21:32:25 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Personel BPBD Kabupaten Kubu Raya menyemprotkan air ke lahan gambut yang terbakar di Dusun Sidomulyo, Desa Limbung, Kecamatan Sungai Raya, Kabupaten Kubu Raya, Kalimantan Barat.</t>
+          <t>Foto udara petugas bersama warga berusaha memadamkan kebakaran lahan yang berada di dekat rumahnya di Desa Sungai Rambutan, Indralaya Utara, Ogan Ili (OI), Sumatera Selatan.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676039/sudah-sepekan-petugas-berjibaku-padamkan-karhutla-di-kubu-raya</t>
+          <t>https://www.antaranews.com/foto/5676076/begini-kondisi-kebakaran-lahan-di-indralaya-utara-sumsel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-Lahan-4.jpg</t>
         </is>
       </c>
     </row>
@@ -1037,28 +1037,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pergelaran kesenian balaganjur pada hari suci umat Hindu di Bali</t>
+          <t>Sudah sepekan petugas berjibaku padamkan karhutla di Kubu Raya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 20:11:17 +0700</t>
+          <t>Sat, 01 Aug 2026 20:51:18 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sejumlah pemuda menampilkan kesenian baleganjur pada Hari Suci Tumpek Krulut di The Blooms Bali, Tabanan, Bali.</t>
+          <t>Personel BPBD Kabupaten Kubu Raya menyemprotkan air ke lahan gambut yang terbakar di Dusun Sidomulyo, Desa Limbung, Kecamatan Sungai Raya, Kabupaten Kubu Raya, Kalimantan Barat.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676007/pergelaran-kesenian-balaganjur-pada-hari-suci-umat-hindu-di-bali</t>
+          <t>https://www.antaranews.com/foto/5676039/sudah-sepekan-petugas-berjibaku-padamkan-karhutla-di-kubu-raya</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bali-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1070,28 +1070,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bungkam PSMS Medan 4-1, Persija Jakarta buka kans ke semifinal Piala Presiden</t>
+          <t>Pergelaran kesenian balaganjur pada hari suci umat Hindu di Bali</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 19:04:32 +0700</t>
+          <t>Sat, 01 Aug 2026 20:11:17 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pesepak bola Persija Jakarta Denis Kolinger (kanan) berebut bola udara dengan pesepak bola PSMS Medan Angelo Meneses (kiri) dan Asyraq Gufron (tengah) pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur.</t>
+          <t>Sejumlah pemuda menampilkan kesenian baleganjur pada Hari Suci Tumpek Krulut di The Blooms Bali, Tabanan, Bali.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5675900/bungkam-psms-medan-4-1-persija-jakarta-buka-kans-ke-semifinal-piala-presiden</t>
+          <t>https://www.antaranews.com/foto/5676007/pergelaran-kesenian-balaganjur-pada-hari-suci-umat-hindu-di-bali</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bola-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bali-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1103,28 +1103,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pemasangan jaring apung penahan sampah di Sungai Lestari</t>
+          <t>Bungkam PSMS Medan 4-1, Persija Jakarta buka kans ke semifinal Piala Presiden</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 18:17:45 +0700</t>
+          <t>Sat, 01 Aug 2026 19:04:32 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Relawan sungai memasang jaring terapung penahan sampah atau trash boom di Sungai Jenes, Pajang, Laweyan, Solo, Jawa Tengah, Sabtu (1/8/2026). Pemkot Solo bekerja sama dengan United Nations Development Programme (UNDP) dan Clean Rivers meluncurkan program penanganan sampah Sungai Lestari dengan skema sampah yang diambil dari hulu sungai Kota Solo akan langsung dipilah dan diolah oleh mitra lokal hingga diharapkan mampu menciptakan sungai yang yang bersih sekaligus upaya mengurangi beban kuota sampah di TPA Putri Cempo. ANTARA FOTO/Mohammad Ayudha/YU</t>
+          <t>Pesepak bola Persija Jakarta Denis Kolinger (kanan) berebut bola udara dengan pesepak bola PSMS Medan Angelo Meneses (kiri) dan Asyraq Gufron (tengah) pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5675871/pemasangan-jaring-apung-penahan-sampah-di-sungai-lestari</t>
+          <t>https://www.antaranews.com/foto/5675900/bungkam-psms-medan-4-1-persija-jakarta-buka-kans-ke-semifinal-piala-presiden</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/pemasangan-trash-boom-penahan-sampah-010826-yud-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bola-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1136,28 +1136,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Begini kemeriahan Jakarta Watersport Festival 2026 di Danau Sunter</t>
+          <t>Pemasangan jaring apung penahan sampah di Sungai Lestari</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 18:01:11 +0700</t>
+          <t>Sat, 01 Aug 2026 18:17:45 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Peserta beradu kecepatan saat mengikuti lomba perahu naga pada Jakarta Watersport Festival 2026 di Danau Sunter, Jakarta.</t>
+          <t>Relawan sungai memasang jaring terapung penahan sampah atau trash boom di Sungai Jenes, Pajang, Laweyan, Solo, Jawa Tengah, Sabtu (1/8/2026). Pemkot Solo bekerja sama dengan United Nations Development Programme (UNDP) dan Clean Rivers meluncurkan program penanganan sampah Sungai Lestari dengan skema sampah yang diambil dari hulu sungai Kota Solo akan langsung dipilah dan diolah oleh mitra lokal hingga diharapkan mampu menciptakan sungai yang yang bersih sekaligus upaya mengurangi beban kuota sampah di TPA Putri Cempo. ANTARA FOTO/Mohammad Ayudha/YU</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5675857/begini-kemeriahan-jakarta-watersport-festival-2026-di-danau-sunter</t>
+          <t>https://www.antaranews.com/foto/5675871/pemasangan-jaring-apung-penahan-sampah-di-sungai-lestari</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Jakarta-Watersport-Festival-2026-182026-pma-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/pemasangan-trash-boom-penahan-sampah-010826-yud-3.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-01.xlsx
+++ b/data/berita_antara_2026-08-01.xlsx
@@ -537,462 +537,462 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
+          <t>10 kebiasaan kecil yang bisa meningkatkan kualitas hidup sehari-hari</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
+          <t>Sat, 01 Aug 2026 14:53:11 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
+          <t>Menjalani hidup yang lebih baik tidak selalu membutuhkan perubahan besar. Justru, kebiasaan-kebiasaan kecil yang ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
+          <t>https://www.antaranews.com/berita/5675683/10-kebiasaan-kecil-yang-bisa-meningkatkan-kualitas-hidup-sehari-hari</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/24/skrining-kebugaran-jasmani-asn-kota-bogor-2810969.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
+          <t>Pergelaran kesenian balaganjur pada hari suci umat Hindu di Bali</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
+          <t>Sat, 01 Aug 2026 20:11:17 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
+          <t>Sejumlah pemuda menampilkan kesenian baleganjur pada Hari Suci Tumpek Krulut di The Blooms Bali, Tabanan, Bali.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
+          <t>https://www.antaranews.com/foto/5676007/pergelaran-kesenian-balaganjur-pada-hari-suci-umat-hindu-di-bali</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bali-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
+          <t>Bungkam PSMS Medan 4-1, Persija Jakarta buka kans ke semifinal Piala Presiden</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
+          <t>Sat, 01 Aug 2026 19:04:32 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
+          <t>Pesepak bola Persija Jakarta Denis Kolinger (kanan) berebut bola udara dengan pesepak bola PSMS Medan Angelo Meneses (kiri) dan Asyraq Gufron (tengah) pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
+          <t>https://www.antaranews.com/foto/5675900/bungkam-psms-medan-4-1-persija-jakarta-buka-kans-ke-semifinal-piala-presiden</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bola-3.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
+          <t>Pemasangan jaring apung penahan sampah di Sungai Lestari</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
+          <t>Sat, 01 Aug 2026 18:17:45 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
+          <t>Relawan sungai memasang jaring terapung penahan sampah atau trash boom di Sungai Jenes, Pajang, Laweyan, Solo, Jawa Tengah, Sabtu (1/8/2026). Pemkot Solo bekerja sama dengan United Nations Development Programme (UNDP) dan Clean Rivers meluncurkan program penanganan sampah Sungai Lestari dengan skema sampah yang diambil dari hulu sungai Kota Solo akan langsung dipilah dan diolah oleh mitra lokal hingga diharapkan mampu menciptakan sungai yang yang bersih sekaligus upaya mengurangi beban kuota sampah di TPA Putri Cempo. ANTARA FOTO/Mohammad Ayudha/YU</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
+          <t>https://www.antaranews.com/foto/5675871/pemasangan-jaring-apung-penahan-sampah-di-sungai-lestari</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/pemasangan-trash-boom-penahan-sampah-010826-yud-3.jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
+          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
+          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
+          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
+          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
+          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
+          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
+          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
+          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
+          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
+          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
+          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
+          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
+          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
+          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
+          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
+          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
+          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
+          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
+          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
+          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
+          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
+          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
+          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
+          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10 kebiasaan kecil yang bisa meningkatkan kualitas hidup sehari-hari</t>
+          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:53:11 +0700</t>
+          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Menjalani hidup yang lebih baik tidak selalu membutuhkan perubahan besar. Justru, kebiasaan-kebiasaan kecil yang ...</t>
+          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675683/10-kebiasaan-kecil-yang-bisa-meningkatkan-kualitas-hidup-sehari-hari</t>
+          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/24/skrining-kebugaran-jasmani-asn-kota-bogor-2810969.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
+          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
+          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
+          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
+          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
+          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
+          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
+          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
+          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
+          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
+          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
+          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
         </is>
       </c>
     </row>
@@ -1004,28 +1004,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Begini kondisi kebakaran lahan di Indralaya Utara Sumsel</t>
+          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 21:32:25 +0700</t>
+          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foto udara petugas bersama warga berusaha memadamkan kebakaran lahan yang berada di dekat rumahnya di Desa Sungai Rambutan, Indralaya Utara, Ogan Ili (OI), Sumatera Selatan.</t>
+          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676076/begini-kondisi-kebakaran-lahan-di-indralaya-utara-sumsel</t>
+          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-Lahan-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1037,28 +1037,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sudah sepekan petugas berjibaku padamkan karhutla di Kubu Raya</t>
+          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 20:51:18 +0700</t>
+          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Personel BPBD Kabupaten Kubu Raya menyemprotkan air ke lahan gambut yang terbakar di Dusun Sidomulyo, Desa Limbung, Kecamatan Sungai Raya, Kabupaten Kubu Raya, Kalimantan Barat.</t>
+          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676039/sudah-sepekan-petugas-berjibaku-padamkan-karhutla-di-kubu-raya</t>
+          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1070,28 +1070,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pergelaran kesenian balaganjur pada hari suci umat Hindu di Bali</t>
+          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 20:11:17 +0700</t>
+          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sejumlah pemuda menampilkan kesenian baleganjur pada Hari Suci Tumpek Krulut di The Blooms Bali, Tabanan, Bali.</t>
+          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676007/pergelaran-kesenian-balaganjur-pada-hari-suci-umat-hindu-di-bali</t>
+          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bali-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1103,28 +1103,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bungkam PSMS Medan 4-1, Persija Jakarta buka kans ke semifinal Piala Presiden</t>
+          <t>Begini kondisi kebakaran lahan di Indralaya Utara Sumsel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 19:04:32 +0700</t>
+          <t>Sat, 01 Aug 2026 21:32:25 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pesepak bola Persija Jakarta Denis Kolinger (kanan) berebut bola udara dengan pesepak bola PSMS Medan Angelo Meneses (kiri) dan Asyraq Gufron (tengah) pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur.</t>
+          <t>Foto udara petugas bersama warga berusaha memadamkan kebakaran lahan yang berada di dekat rumahnya di Desa Sungai Rambutan, Indralaya Utara, Ogan Ili (OI), Sumatera Selatan.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5675900/bungkam-psms-medan-4-1-persija-jakarta-buka-kans-ke-semifinal-piala-presiden</t>
+          <t>https://www.antaranews.com/foto/5676076/begini-kondisi-kebakaran-lahan-di-indralaya-utara-sumsel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bola-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-Lahan-4.jpg</t>
         </is>
       </c>
     </row>
@@ -1136,28 +1136,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pemasangan jaring apung penahan sampah di Sungai Lestari</t>
+          <t>Sudah sepekan petugas berjibaku padamkan karhutla di Kubu Raya</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 18:17:45 +0700</t>
+          <t>Sat, 01 Aug 2026 20:51:18 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Relawan sungai memasang jaring terapung penahan sampah atau trash boom di Sungai Jenes, Pajang, Laweyan, Solo, Jawa Tengah, Sabtu (1/8/2026). Pemkot Solo bekerja sama dengan United Nations Development Programme (UNDP) dan Clean Rivers meluncurkan program penanganan sampah Sungai Lestari dengan skema sampah yang diambil dari hulu sungai Kota Solo akan langsung dipilah dan diolah oleh mitra lokal hingga diharapkan mampu menciptakan sungai yang yang bersih sekaligus upaya mengurangi beban kuota sampah di TPA Putri Cempo. ANTARA FOTO/Mohammad Ayudha/YU</t>
+          <t>Personel BPBD Kabupaten Kubu Raya menyemprotkan air ke lahan gambut yang terbakar di Dusun Sidomulyo, Desa Limbung, Kecamatan Sungai Raya, Kabupaten Kubu Raya, Kalimantan Barat.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5675871/pemasangan-jaring-apung-penahan-sampah-di-sungai-lestari</t>
+          <t>https://www.antaranews.com/foto/5676039/sudah-sepekan-petugas-berjibaku-padamkan-karhutla-di-kubu-raya</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/pemasangan-trash-boom-penahan-sampah-010826-yud-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-2.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-01.xlsx
+++ b/data/berita_antara_2026-08-01.xlsx
@@ -669,99 +669,99 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
+          <t>Begini kondisi kebakaran lahan di Indralaya Utara Sumsel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
+          <t>Sat, 01 Aug 2026 21:32:25 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
+          <t>Foto udara petugas bersama warga berusaha memadamkan kebakaran lahan yang berada di dekat rumahnya di Desa Sungai Rambutan, Indralaya Utara, Ogan Ili (OI), Sumatera Selatan.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
+          <t>https://www.antaranews.com/foto/5676076/begini-kondisi-kebakaran-lahan-di-indralaya-utara-sumsel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-Lahan-4.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
+          <t>Sudah sepekan petugas berjibaku padamkan karhutla di Kubu Raya</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
+          <t>Sat, 01 Aug 2026 20:51:18 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
+          <t>Personel BPBD Kabupaten Kubu Raya menyemprotkan air ke lahan gambut yang terbakar di Dusun Sidomulyo, Desa Limbung, Kecamatan Sungai Raya, Kabupaten Kubu Raya, Kalimantan Barat.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
+          <t>https://www.antaranews.com/foto/5676039/sudah-sepekan-petugas-berjibaku-padamkan-karhutla-di-kubu-raya</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
+          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
+          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
+          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
+          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
+          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
+          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
+          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
+          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
         </is>
       </c>
     </row>
@@ -806,259 +806,259 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
+          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
+          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
+          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
+          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
+          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
+          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
+          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
+          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
+          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
+          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
+          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
+          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
+          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
+          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
+          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
+          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
+          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
+          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
+          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
+          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
+          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
+          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
+          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
+          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
+          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
+          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
+          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
+          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
+          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
+          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
         </is>
       </c>
     </row>
@@ -1070,28 +1070,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
+          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
+          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
+          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
+          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1103,28 +1103,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Begini kondisi kebakaran lahan di Indralaya Utara Sumsel</t>
+          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 21:32:25 +0700</t>
+          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Foto udara petugas bersama warga berusaha memadamkan kebakaran lahan yang berada di dekat rumahnya di Desa Sungai Rambutan, Indralaya Utara, Ogan Ili (OI), Sumatera Selatan.</t>
+          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676076/begini-kondisi-kebakaran-lahan-di-indralaya-utara-sumsel</t>
+          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-Lahan-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1136,28 +1136,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sudah sepekan petugas berjibaku padamkan karhutla di Kubu Raya</t>
+          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 20:51:18 +0700</t>
+          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Personel BPBD Kabupaten Kubu Raya menyemprotkan air ke lahan gambut yang terbakar di Dusun Sidomulyo, Desa Limbung, Kecamatan Sungai Raya, Kabupaten Kubu Raya, Kalimantan Barat.</t>
+          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676039/sudah-sepekan-petugas-berjibaku-padamkan-karhutla-di-kubu-raya</t>
+          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-01.xlsx
+++ b/data/berita_antara_2026-08-01.xlsx
@@ -735,66 +735,66 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
+          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
+          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
+          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
+          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
+          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
+          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
+          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
+          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
         </is>
       </c>
     </row>
@@ -806,28 +806,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
+          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
+          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
+          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
+          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
         </is>
       </c>
     </row>
@@ -839,28 +839,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
+          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
+          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
+          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
+          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
         </is>
       </c>
     </row>
@@ -872,61 +872,61 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
+          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
+          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
+          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
+          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
+          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
+          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
+          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
         </is>
       </c>
     </row>
@@ -938,94 +938,94 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
+          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
+          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
+          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
+          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
+          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
+          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
+          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
+          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
+          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
+          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
+          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
+          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
         </is>
       </c>
     </row>
@@ -1037,61 +1037,61 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
+          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
+          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
+          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
+          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
+          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
+          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
+          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
+          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
         </is>
       </c>
     </row>
@@ -1103,28 +1103,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
+          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
+          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
+          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1136,28 +1136,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aston Villa kalahkan Indonesia All Stars dengan skor 3-1</t>
+          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 21:43:10 +0700</t>
+          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pesepak bola Indonesia All Stars Oliver Leeming (kanan) melakukan duel udara dengan pesepak bola Aston Villa Triston Rowe (kedua kanan) pada pertandingan bertajuk Aston Villa Pre-Season Tour Indonesia 2026 di Stadion Utama Gelora Bung Karno, Senayan, Jakarta, Sabtu (1/8/2026). Indonesia All Stars dikalahkan Aston Villa dengan skor 1-3 ANTARA FOTO/Fauzan/YU</t>
+          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676091/aston-villa-kalahkan-indonesia-all-stars-dengan-skor-3-1</t>
+          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-01.xlsx
+++ b/data/berita_antara_2026-08-01.xlsx
@@ -768,33 +768,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
+          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
+          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
+          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
+          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
         </is>
       </c>
     </row>
@@ -806,28 +806,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LPDB siapkan KDKMP di Papua agar layak memperoleh pembiayaan</t>
+          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 16:45:47 +0700</t>
+          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi memperkuat kapasitas 15 Koperasi Desa/Kelurahan Merah Putih (KDKMP) ...</t>
+          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675779/lpdb-siapkan-kdkmp-di-papua-agar-layak-memperoleh-pembiayaan</t>
+          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
         </is>
       </c>
     </row>
@@ -839,28 +839,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Apkasi usulkan formula DBH berbasis produksi perkuat fiskal daerah</t>
+          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:59:10 +0700</t>
+          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Asosiasi Pemerintah Kabupaten Seluruh Indonesia (Apkasi) mengusulkan penyempurnaan formula Dana Bagi Hasil (DBH) sektor ...</t>
+          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675695/apkasi-usulkan-formula-dbh-berbasis-produksi-perkuat-fiskal-daerah</t>
+          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
         </is>
       </c>
     </row>
@@ -872,94 +872,94 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gubernur Khofifah beri keringanan pajak kendaraan selama Agustus 2026</t>
+          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 10:03:39 +0700</t>
+          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memberikan keringanan pembayaran pajak kendaraan selama periode 1-31 ...</t>
+          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675479/gubernur-khofifah-beri-keringanan-pajak-kendaraan-selama-agustus-2026</t>
+          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Maybank Indonesia bukukan laba bersih Rp698 miliar semester I-2026</t>
+          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 00:09:43 +0700</t>
+          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PT Bank Maybank Indonesia Tbk (Maybank Indonesia) membukukan laba bersih sebesar Rp698 miliar pada semester I-2026, ...</t>
+          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675279/maybank-indonesia-bukukan-laba-bersih-rp698-miliar-semester-i-2026</t>
+          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
+          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
+          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
+          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
+          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
         </is>
       </c>
     </row>
@@ -971,94 +971,94 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
+          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
+          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
+          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
+          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
+          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
+          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
+          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
+          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
+          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
+          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
+          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
+          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
         </is>
       </c>
     </row>
@@ -1070,61 +1070,61 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
+          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
+          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
+          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
+          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
+          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
+          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
+          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
+          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
         </is>
       </c>
     </row>
@@ -1136,28 +1136,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zikir dan doa kebangsaan sambut HUT ke-81 RI</t>
+          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:00:30 +0700</t>
+          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umat Islam mengikuti zikir dan doa kebangsaan 2006 di kawasan Monas, Jakarta.</t>
+          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676104/zikir-dan-doa-kebangsaan-sambut-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-01.xlsx
+++ b/data/berita_antara_2026-08-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -429,6 +429,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +468,11 @@
           <t>URL Gambar</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,7 @@
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-kapal-Prince-Soya-di-Pelabuhan-Samarinda-010826-Pelindo-AP-2.jpg</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,6 +540,7 @@
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Jakarta-Watersport-Festival-2026-182026-pma-2.jpg</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -566,6 +574,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/06/24/skrining-kebugaran-jasmani-asn-kota-bogor-2810969.jpg</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -599,6 +608,7 @@
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bali-2.jpg</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -632,6 +642,7 @@
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Bola-3.jpg</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -665,6 +676,7 @@
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/pemasangan-trash-boom-penahan-sampah-010826-yud-3.jpg</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -698,6 +710,7 @@
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-Lahan-4.jpg</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -731,6 +744,7 @@
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Kebakaran-2.jpg</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -764,6 +778,7 @@
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Indoesia-All-Star-vs-Aston-Vila-2.jpg</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -797,6 +812,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/WhatsApp-Image-2026-08-01-at-16.36.12.jpeg</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -830,6 +846,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1000175928.jpg</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -863,6 +880,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1311386.jpg</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -896,6 +914,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2025/05/02/Sentra-Senayan-Picture-Night-Time-1_2.jpg</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -929,70 +948,77 @@
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Zikir-3.jpg</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
+          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
+          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
+          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
+          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
+          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
+          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
+          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
+          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1004,94 +1030,109 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
+          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
+          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
+          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
+          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
+          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
+          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
+          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
+          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
+          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
+          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
+          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
+          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
@@ -1103,66 +1144,76 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
+          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
+          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
+          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
+          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kalahkan Port FC 2-1, Persebaya melaju ke semifinal Piala Presiden 2026</t>
+          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 22:35:05 +0700</t>
+          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pesepak bola Persebaya Surabaya Miguel Pereira (bawah) bersama rekannya Koko Ari Araya (atas) berselebrasi usai mencetak gol ke gawang Port FC pada pertandingan Grup B Piala Presiden 2026 di Stadion Gelora Bung Tomo, Surabaya, Jawa Timur, Sabtu (1/8/2026). Persebaya Surabaya lolos ke semifinal usai mengalahkan Port FC dengan skor 2-1. ANTARA FOTO/Rizal Hanafi/YU</t>
+          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5676144/kalahkan-port-fc-2-1-persebaya-melaju-ke-semifinal-piala-presiden-2026</t>
+          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/01/Persebaya-Menang-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:H22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-01.xlsx
+++ b/data/berita_antara_2026-08-01.xlsx
@@ -987,33 +987,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
+          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
+          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
+          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
+          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1025,33 +1025,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
+          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
+          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
+          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
+          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1063,33 +1063,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
+          <t>Jam buka GIIAS 2026 lengkap, simak jadwal operasional dan harga tiket</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
+          <t>Sat, 01 Aug 2026 14:57:18 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
+          <t>Pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
+          <t>https://otomotif.antaranews.com/berita/5675691/jam-buka-giias-2026-lengkap-simak-jadwal-operasional-dan-harga-tiket</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_1452.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1101,33 +1101,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
+          <t>Pemerintah RI targetkan stop impor garam per akhir 2027</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
+          <t>Sat, 01 Aug 2026 07:13:28 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
+          <t>Pemerintah Republik Indonesia (RI) menargetkan untuk menyetop impor garam per akhir 2027 sebagai bagian dari upaya ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
+          <t>https://www.antaranews.com/berita/5675401/pemerintah-ri-targetkan-stop-impor-garam-per-akhir-2027</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000023_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1139,33 +1139,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6 wisata alam di Bogor yang ramah lansia, nyaman dan mudah diakses</t>
+          <t>IMIP raih penghargaan utama ESG IDX Channel 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:08:07 +0700</t>
+          <t>Sat, 01 Aug 2026 07:10:53 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kota Bogor dan wilayah sekitarnya menawarkan sejumlah destinasi wisata alam yang cocok dikunjungi bersama lansia. ...</t>
+          <t>Kawasan Industri Indonesia Morowali Industrial Park (IMIP) berhasil meraih Penghargaan Utama ESG untuk sektor ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675711/6-wisata-alam-di-bogor-yang-ramah-lansia-nyaman-dan-mudah-diakses</t>
+          <t>https://www.antaranews.com/berita/5675396/imip-raih-penghargaan-utama-esg-idx-channel-2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/hut-krb-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/CjkinzN000028_20260731_CBMFN0A001.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1177,33 +1177,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cara menghilangkan rasa panas di tangan akibat cabai</t>
+          <t>Hukum mengedarkan kotak amal saat khutbah Jumat, makruh atau boleh?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sat, 01 Aug 2026 15:02:01 +0700</t>
+          <t>Sat, 01 Aug 2026 14:48:54 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sensasi panas pada tangan setelah memegang atau mengolah cabai sering membuat tidak nyaman. Kondisi tersebut terjadi ...</t>
+          <t>Mengedarkan kotak amal ketika khutbah Jumat berlangsung menjadi kebiasaan yang masih ditemukan di sejumlah masjid. ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5675701/cara-menghilangkan-rasa-panas-di-tangan-akibat-cabai</t>
+          <t>https://www.antaranews.com/berita/5675680/hukum-mengedarkan-kotak-amal-saat-khutbah-jumat-makruh-atau-boleh</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/10/04/cuci-tangan.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/20/shalat-jumat-pertama-ramadhan-di-masjid-kuno-indrapuri-aceh-2734630.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
